--- a/data/Pharmacie.xlsx
+++ b/data/Pharmacie.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\WAILS_GO_DEV\Wails1\leopard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{770C66D5-2494-4130-A7A5-8CC8A823CD1A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{682FCFFD-2C57-457A-8A95-7ED481DABF2C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5280" yWindow="4290" windowWidth="28800" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rapport au MSSS - Services ..." sheetId="1" r:id="rId1"/>
@@ -1765,9 +1765,6 @@
     <t>HeuresOuvertDim</t>
   </si>
   <si>
-    <t>HeureOuverLundi</t>
-  </si>
-  <si>
     <t>Nom de lorganisation</t>
   </si>
   <si>
@@ -1826,6 +1823,9 @@
   </si>
   <si>
     <t>HeureFermetureSamedi</t>
+  </si>
+  <si>
+    <t>OuverLundi</t>
   </si>
 </sst>
 </file>
@@ -1902,7 +1902,7 @@
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="DimancheOuvert"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="HeureOuvertureDimanche"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="HeuresOuvertDim"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="HeureOuverLundi"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="OuverLundi"/>
     <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="HeureOuvertureLundi"/>
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="HeureFermetureLundi"/>
     <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="MardiOuvert"/>
@@ -2252,7 +2252,7 @@
   <sheetData>
     <row r="1" spans="1:28">
       <c r="A1" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B1" t="s">
         <v>574</v>
@@ -2273,67 +2273,67 @@
         <v>577</v>
       </c>
       <c r="H1" t="s">
+        <v>580</v>
+      </c>
+      <c r="I1" t="s">
         <v>581</v>
-      </c>
-      <c r="I1" t="s">
-        <v>582</v>
       </c>
       <c r="J1" t="s">
         <v>578</v>
       </c>
       <c r="K1" t="s">
-        <v>579</v>
+        <v>599</v>
       </c>
       <c r="L1" t="s">
+        <v>582</v>
+      </c>
+      <c r="M1" t="s">
         <v>583</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>584</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>585</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>586</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>587</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>588</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>589</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>590</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>591</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>592</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>593</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>594</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>595</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>596</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>597</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>598</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="2" spans="1:28">
